--- a/data/output/bfretro.xlsx
+++ b/data/output/bfretro.xlsx
@@ -36,72 +36,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Palossand A+SB/ST 1/12/13</t>
+          <t>Blastoise RO+SkB/HC 1/12/15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ghost/ground</t>
+          <t>water/none</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Greedent MS+BS/TBl 4/14/14</t>
+          <t>Kingdra DB+Sw/O 1/13/15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>normal/none</t>
+          <t>water/dragon</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Crustle FC+XS/RW 0/14/15</t>
+          <t>Kommo-o DT+UH/ClS 3/15/13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>bug/rock</t>
+          <t>dragon/fighting</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cetitan PS+ISp/SP 1/14/11</t>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ice/none</t>
+          <t>psychic/none</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Annihilape LK+RF/CC 3/11/15</t>
+          <t>Skeledirge I+TSo/SB 0/15/15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fighting/ghost</t>
+          <t>fire/ghost</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Roserade PSt+WBF/LfS 0/14/12</t>
+          <t>Golisopod FC+XS/AJ 1/14/15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>grass/poison</t>
+          <t>bug/water</t>
         </is>
       </c>
     </row>
@@ -131,7 +131,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>377.4611398963731</v>
+        <v>227.57894736842104</v>
       </c>
     </row>
     <row r="3">
@@ -141,7 +141,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>179.29403210772855</v>
+        <v>197.9092756412052</v>
       </c>
     </row>
     <row r="4">
@@ -151,7 +151,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>88.48659003831418</v>
+        <v>181.0</v>
       </c>
     </row>
     <row r="5">
@@ -161,7 +161,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>192.2466590025347</v>
+        <v>200.04721638481848</v>
       </c>
     </row>
     <row r="6">
@@ -171,7 +171,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>807.2518518518518</v>
+        <v>819.2777777777777</v>
       </c>
     </row>
     <row r="7">
@@ -181,7 +181,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>118</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.8740740740740741</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="9">
@@ -201,7 +201,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>45</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -211,7 +211,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>741.6962962962963</v>
+        <v>752.6111111111111</v>
       </c>
     </row>
     <row r="11">
@@ -261,7 +261,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>135</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>135</v>
+        <v>16</v>
       </c>
     </row>
     <row r="17">
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>100</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -321,7 +321,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>96.3</v>
+        <v>88.6</v>
       </c>
     </row>
     <row r="22">
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>69.376</v>
+        <v>80.25454545454545</v>
       </c>
     </row>
     <row r="23">
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>26.7</v>
+        <v>66.9</v>
       </c>
     </row>
     <row r="24">
@@ -363,7 +363,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>79.35000000000001</v>
+        <v>77.88333333333334</v>
       </c>
     </row>
     <row r="26">
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.0</v>
+        <v>0.1111111111111111</v>
       </c>
     </row>
     <row r="28">
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>135</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>686.7045454545453</v>
+        <v>715.1666666666666</v>
       </c>
     </row>
   </sheetData>
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -479,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -516,7 +516,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Palossand A+SB/ST 1/12/13, Cetitan PS+ISp/SP 1/14/11, Roserade PSt+WBF/LfS 0/14/12</t>
+          <t>Blastoise RO+SkB/HC 1/12/15, Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13</t>
         </is>
       </c>
     </row>
@@ -526,7 +526,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Palossand A+SB/ST 1/12/13, Greedent MS+BS/TBl 4/14/14, Annihilape LK+RF/CC 3/11/15</t>
+          <t>Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13, Skeledirge I+TSo/SB 0/15/15</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Greedent MS+BS/TBl 4/14/14, Cetitan PS+ISp/SP 1/14/11, Annihilape LK+RF/CC 3/11/15</t>
+          <t>Blastoise RO+SkB/HC 1/12/15, Kingdra DB+Sw/O 1/13/15, Grumpig Psy+SB/DyP 6/14/13</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Crustle FC+XS/RW 0/14/15, Cetitan PS+ISp/SP 1/14/11, Annihilape LK+RF/CC 3/11/15</t>
+          <t>Blastoise RO+SkB/HC 1/12/15, Grumpig Psy+SB/DyP 6/14/13, Golisopod FC+XS/AJ 1/14/15</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,57 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Greedent MS+BS/TBl 4/14/14, Crustle FC+XS/RW 0/14/15, Annihilape LK+RF/CC 3/11/15</t>
+          <t>Grumpig Psy+SB/DyP 6/14/13, Skeledirge I+TSo/SB 0/15/15, Golisopod FC+XS/AJ 1/14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Blastoise RO+SkB/HC 1/12/15, Kingdra DB+Sw/O 1/13/15, Kommo-o DT+UH/ClS 3/15/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kingdra DB+Sw/O 1/13/15, Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kingdra DB+Sw/O 1/13/15, Kommo-o DT+UH/ClS 3/15/13, Skeledirge I+TSo/SB 0/15/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13, Golisopod FC+XS/AJ 1/14/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Blastoise RO+SkB/HC 1/12/15, Kingdra DB+Sw/O 1/13/15, Golisopod FC+XS/AJ 1/14/15</t>
         </is>
       </c>
     </row>
@@ -592,180 +642,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kingdra DB+Sw/O 0/15/15</t>
+          <t>Kommo-o DT+ClS/UH 4/12/13</t>
         </is>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Drifblim A+IW/SB 1/15/15</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>0</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Tentacruel Ac+Sc/Pbk 0/13/15</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>0</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Kommo-o DT+ClS/UH 0/11/14</t>
-        </is>
-      </c>
-      <c r="B5">
-        <v>0</v>
-      </c>
-      <c r="C5">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Gyarados (Shadow) DB+AT/Tw 0/15/14</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Golisopod FC+XS/AJ 1/14/15</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Giratina (Origin) SC+SB/DgP 1/12/13</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>0</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Giratina (Origin) SC+SB/DgP 1/12/13</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Poliwrath MS+IW/DyP 0/14/14</t>
-        </is>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Walrein PS+ISp/Eq 0/15/15</t>
-        </is>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>0-shield only Grumpig Psy+SB/DyP 6/14/13 | 1-shield only Grumpig Psy+SB/DyP 6/14/13</t>
         </is>
       </c>
     </row>

--- a/data/output/bfretro.xlsx
+++ b/data/output/bfretro.xlsx
@@ -36,72 +36,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Blastoise RO+SkB/HC 1/12/15</t>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>water/none</t>
+          <t>grass/poison</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kingdra DB+Sw/O 1/13/15</t>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>water/dragon</t>
+          <t>dragon/fighting</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Kommo-o DT+UH/ClS 3/15/13</t>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>dragon/fighting</t>
+          <t>ice/flying</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+          <t>Kyurem DB+G/DC 5/8/14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>psychic/none</t>
+          <t>dragon/ice</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Skeledirge I+TSo/SB 0/15/15</t>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fire/ghost</t>
+          <t>electric/none</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Golisopod FC+XS/AJ 1/14/15</t>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bug/water</t>
+          <t>psychic/none</t>
         </is>
       </c>
     </row>
@@ -131,7 +131,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>227.57894736842104</v>
+        <v>254.4375</v>
       </c>
     </row>
     <row r="3">
@@ -141,7 +141,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>197.9092756412052</v>
+        <v>189.0179404607102</v>
       </c>
     </row>
     <row r="4">
@@ -151,7 +151,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>181.0</v>
+        <v>167.4896265560166</v>
       </c>
     </row>
     <row r="5">
@@ -161,7 +161,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>200.04721638481848</v>
+        <v>196.1940450956081</v>
       </c>
     </row>
     <row r="6">
@@ -171,7 +171,7 @@
         </is>
       </c>
       <c r="B6">
-        <v>819.2777777777777</v>
+        <v>843.6666666666666</v>
       </c>
     </row>
     <row r="7">
@@ -181,7 +181,7 @@
         </is>
       </c>
       <c r="B7">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.8888888888888888</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="9">
@@ -201,7 +201,7 @@
         </is>
       </c>
       <c r="B9">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
@@ -211,7 +211,7 @@
         </is>
       </c>
       <c r="B10">
-        <v>752.6111111111111</v>
+        <v>782.5555555555555</v>
       </c>
     </row>
     <row r="11">
@@ -261,7 +261,7 @@
         </is>
       </c>
       <c r="B15">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -271,7 +271,7 @@
         </is>
       </c>
       <c r="B16">
-        <v>16</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="B17">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18">
@@ -321,7 +321,7 @@
         </is>
       </c>
       <c r="B21">
-        <v>88.6</v>
+        <v>77.0</v>
       </c>
     </row>
     <row r="22">
@@ -331,7 +331,7 @@
         </is>
       </c>
       <c r="B22">
-        <v>80.25454545454545</v>
+        <v>68.9875</v>
       </c>
     </row>
     <row r="23">
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="B23">
-        <v>66.9</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="24">
@@ -363,7 +363,7 @@
         </is>
       </c>
       <c r="B25">
-        <v>77.88333333333334</v>
+        <v>66.31666666666666</v>
       </c>
     </row>
     <row r="26">
@@ -373,7 +373,7 @@
         </is>
       </c>
       <c r="B26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -383,7 +383,7 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.1111111111111111</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="28">
@@ -393,7 +393,7 @@
         </is>
       </c>
       <c r="B28">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -403,7 +403,7 @@
         </is>
       </c>
       <c r="B29">
-        <v>715.1666666666666</v>
+        <v>691.9722222222223</v>
       </c>
     </row>
   </sheetData>
@@ -445,7 +445,7 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -462,7 +462,7 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -479,7 +479,7 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -506,7 +506,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Members</t>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Switch</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Closer</t>
         </is>
       </c>
     </row>
@@ -516,7 +531,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Blastoise RO+SkB/HC 1/12/15, Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
         </is>
       </c>
     </row>
@@ -526,7 +556,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13, Skeledirge I+TSo/SB 0/15/15</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
         </is>
       </c>
     </row>
@@ -536,7 +581,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Blastoise RO+SkB/HC 1/12/15, Kingdra DB+Sw/O 1/13/15, Grumpig Psy+SB/DyP 6/14/13</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
         </is>
       </c>
     </row>
@@ -546,7 +606,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blastoise RO+SkB/HC 1/12/15, Grumpig Psy+SB/DyP 6/14/13, Golisopod FC+XS/AJ 1/14/15</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
         </is>
       </c>
     </row>
@@ -556,7 +631,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13, Skeledirge I+TSo/SB 0/15/15, Golisopod FC+XS/AJ 1/14/15</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
         </is>
       </c>
     </row>
@@ -566,7 +656,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Blastoise RO+SkB/HC 1/12/15, Kingdra DB+Sw/O 1/13/15, Kommo-o DT+UH/ClS 3/15/13</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
         </is>
       </c>
     </row>
@@ -576,7 +681,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kingdra DB+Sw/O 1/13/15, Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
         </is>
       </c>
     </row>
@@ -586,7 +706,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kingdra DB+Sw/O 1/13/15, Kommo-o DT+UH/ClS 3/15/13, Skeledirge I+TSo/SB 0/15/15</t>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
         </is>
       </c>
     </row>
@@ -596,7 +731,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kommo-o DT+UH/ClS 3/15/13, Grumpig Psy+SB/DyP 6/14/13, Golisopod FC+XS/AJ 1/14/15</t>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
         </is>
       </c>
     </row>
@@ -606,7 +756,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Blastoise RO+SkB/HC 1/12/15, Kingdra DB+Sw/O 1/13/15, Golisopod FC+XS/AJ 1/14/15</t>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
         </is>
       </c>
     </row>
@@ -642,18 +807,162 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kommo-o DT+ClS/UH 4/12/13</t>
+          <t>Kingdra DB+Sw/O 0/15/15</t>
         </is>
       </c>
       <c r="B2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-shield only Grumpig Psy+SB/DyP 6/14/13 | 1-shield only Grumpig Psy+SB/DyP 6/14/13</t>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cetitan PS+ISp/SP 4/15/15</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Toucannon Pk+BBl/DrlP 2/15/14</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Virizion DK+LB/SSw 1/15/12</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Blastoise RO+HC/SkB 5/15/15</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Gliscor (Shadow) WA+ST/NS 0/14/15</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Gliscor (Shadow) WA+Acr/ST 0/14/15</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Blastoise RO+HC/IB 5/15/15</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Gliscor (Shadow) WA+Acr/NS 0/14/15</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
     </row>

--- a/data/output/bfretro.xlsx
+++ b/data/output/bfretro.xlsx
@@ -7,6 +7,10 @@
     <sheet name="Coverage" sheetId="3" r:id="rId3"/>
     <sheet name="Safe Cores" sheetId="4" r:id="rId4"/>
     <sheet name="Threats" sheetId="5" r:id="rId5"/>
+    <sheet name="Lineups" sheetId="6" r:id="rId6"/>
+    <sheet name="Lineup Resources" sheetId="7" r:id="rId7"/>
+    <sheet name="Bench Utility" sheetId="8" r:id="rId8"/>
+    <sheet name="Bench Warnings" sheetId="9" r:id="rId9"/>
   </sheets>
 </workbook>
 </file>
@@ -177,67 +181,67 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>dominate_count</t>
+          <t>defensive_type_score</t>
         </is>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>-15.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>dominate_rate</t>
+          <t>dominate_count</t>
         </is>
       </c>
       <c r="B8">
-        <v>0.8148148148148148</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>full_col_coverage</t>
+          <t>dominate_rate</t>
         </is>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>0.8148148148148148</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mean_best_score</t>
+          <t>full_col_coverage</t>
         </is>
       </c>
       <c r="B10">
-        <v>782.5555555555555</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>no_cover_pairs</t>
+          <t>legacy_full_roster_dominate_count</t>
         </is>
       </c>
       <c r="B11">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>no_cover_rate</t>
+          <t>legacy_full_roster_mean_best_score</t>
         </is>
       </c>
       <c r="B12">
-        <v>0.0</v>
+        <v>782.5555555555555</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>overwhelming_count</t>
+          <t>legacy_full_roster_overwhelming_count</t>
         </is>
       </c>
       <c r="B13">
@@ -247,162 +251,262 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>overwhelming_rate</t>
+          <t>lineup_best_score</t>
         </is>
       </c>
       <c r="B14">
-        <v>0.0</v>
+        <v>759.2592592592592</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>pair_coverage</t>
+          <t>lineup_objective_score</t>
         </is>
       </c>
       <c r="B15">
-        <v>27</v>
+        <v>656.2300740740741</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>redundant_coverage_2plus</t>
+          <t>lineup_top_n_mean_score</t>
         </is>
       </c>
       <c r="B16">
-        <v>27</v>
+        <v>748.9085185185186</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>redundant_coverage_3plus</t>
+          <t>lineup_viable_count</t>
         </is>
       </c>
       <c r="B17">
-        <v>21</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>safe_member_floor</t>
+          <t>mean_best_score</t>
         </is>
       </c>
       <c r="B18">
-        <v>90.0</v>
+        <v>782.5555555555555</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>safe_member_target</t>
+          <t>no_cover_pairs</t>
         </is>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>safety_floor_target</t>
+          <t>no_cover_rate</t>
         </is>
       </c>
       <c r="B20">
-        <v>78.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>safety_pool_max</t>
+          <t>offensive_move_score</t>
         </is>
       </c>
       <c r="B21">
-        <v>77.0</v>
+        <v>24.000000000000007</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>safety_pool_mean</t>
+          <t>overwhelming_count</t>
         </is>
       </c>
       <c r="B22">
-        <v>68.9875</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>safety_pool_min</t>
+          <t>overwhelming_rate</t>
         </is>
       </c>
       <c r="B23">
-        <v>44.3</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>safety_priority</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
+          <t>pair_coverage</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>safety_score</t>
+          <t>ranking_aware_score</t>
         </is>
       </c>
       <c r="B25">
-        <v>66.31666666666666</v>
+        <v>0.7222160914154244</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>single_cover_pairs</t>
+          <t>redundant_coverage_2plus</t>
         </is>
       </c>
       <c r="B26">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>single_cover_rate</t>
+          <t>redundant_coverage_3plus</t>
         </is>
       </c>
       <c r="B27">
-        <v>0.0</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>total_pairs</t>
+          <t>safe_member_floor</t>
         </is>
       </c>
       <c r="B28">
-        <v>27</v>
+        <v>90.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>safe_member_target</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>safety_floor_target</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>78.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>safety_pool_max</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>96.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>safety_pool_mean</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>79.1375</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>safety_pool_min</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>68.5</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>safety_priority</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>safety_score</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>81.48333333333333</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>single_cover_pairs</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>single_cover_rate</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>total_pairs</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
           <t>weighted_worst_best_score</t>
         </is>
       </c>
-      <c r="B29">
+      <c r="B39">
         <v>691.9722222222223</v>
       </c>
     </row>
@@ -525,256 +629,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Kommo-o DT+UH/ClS 4/12/13</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Kyurem DB+G/DC 5/8/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Kommo-o DT+UH/ClS 4/12/13</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Articuno PS+IW/Hu 14/13/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Raikou TS+WC/AuS 5/13/13</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Articuno PS+IW/Hu 14/13/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Kommo-o DT+UH/ClS 4/12/13</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Raikou TS+WC/AuS 5/13/13</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Articuno PS+IW/Hu 14/13/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Kyurem DB+G/DC 5/8/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Raikou TS+WC/AuS 5/13/13</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Kyurem DB+G/DC 5/8/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Kommo-o DT+UH/ClS 4/12/13</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Raikou TS+WC/AuS 5/13/13</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Kyurem DB+G/DC 5/8/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ABC</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Articuno PS+IW/Hu 14/13/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Grumpig Psy+SB/DyP 6/14/13</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Kyurem DB+G/DC 5/8/14</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Articuno PS+IW/Hu 14/13/14</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>ABA</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Articuno PS+IW/Hu 14/13/14</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Raikou TS+WC/AuS 5/13/13</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kyurem DB+G/DC 5/8/14</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -968,4 +822,1305 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Lead</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Back 1</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Back 2</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Team Shape</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lineup Score</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Mean Score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Dominating Matchups</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Overwhelming Matchups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F2">
+        <v>760.4527724704012</v>
+      </c>
+      <c r="G2">
+        <v>759.2592592592592</v>
+      </c>
+      <c r="H2">
+        <v>22</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F3">
+        <v>757.1514195652995</v>
+      </c>
+      <c r="G3">
+        <v>756.888888888889</v>
+      </c>
+      <c r="H3">
+        <v>22</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F4">
+        <v>755.3642761351657</v>
+      </c>
+      <c r="G4">
+        <v>754.5925925925926</v>
+      </c>
+      <c r="H4">
+        <v>22</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F5">
+        <v>750.4105351625406</v>
+      </c>
+      <c r="G5">
+        <v>746.9629629629629</v>
+      </c>
+      <c r="H5">
+        <v>22</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F6">
+        <v>749.8906095188852</v>
+      </c>
+      <c r="G6">
+        <v>732.074074074074</v>
+      </c>
+      <c r="H6">
+        <v>23</v>
+      </c>
+      <c r="I6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Grumpig Psy+SB/DyP 6/14/13</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F7">
+        <v>749.0851081833645</v>
+      </c>
+      <c r="G7">
+        <v>746.6296296296296</v>
+      </c>
+      <c r="H7">
+        <v>22</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F8">
+        <v>748.2885158730426</v>
+      </c>
+      <c r="G8">
+        <v>731.4074074074074</v>
+      </c>
+      <c r="H8">
+        <v>23</v>
+      </c>
+      <c r="I8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F9">
+        <v>747.2697234903869</v>
+      </c>
+      <c r="G9">
+        <v>744.3333333333334</v>
+      </c>
+      <c r="H9">
+        <v>23</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kyurem DB+G/DC 5/8/14</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Raikou TS+WC/AuS 5/13/13</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ABA</t>
+        </is>
+      </c>
+      <c r="F10">
+        <v>745.6324756213555</v>
+      </c>
+      <c r="G10">
+        <v>743.1851851851852</v>
+      </c>
+      <c r="H10">
+        <v>23</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kommo-o DT+UH/ClS 4/12/13</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Venusaur (Shadow) VW+Sl/FP 4/14/15</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Articuno PS+IW/Hu 14/13/14</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ABC</t>
+        </is>
+      </c>
+      <c r="F11">
+        <v>745.2828847437744</v>
+      </c>
+      <c r="G11">
+        <v>727.6296296296296</v>
+      </c>
+      <c r="H11">
+        <v>23</v>
+      </c>
+      <c r="I11">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Lineup Rank</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Path</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lead Shield</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Back Shield</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Mean Best Score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dominating Matchups</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Overwhelming Matchups</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>737.8888888888889</v>
+      </c>
+      <c r="F2">
+        <v>7</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>795.3333333333334</v>
+      </c>
+      <c r="F3">
+        <v>8</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>744.5555555555555</v>
+      </c>
+      <c r="F4">
+        <v>7</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>737.8888888888889</v>
+      </c>
+      <c r="F5">
+        <v>7</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>787.4444444444445</v>
+      </c>
+      <c r="F6">
+        <v>8</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>745.3333333333334</v>
+      </c>
+      <c r="F7">
+        <v>7</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>3</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>737.8888888888889</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>754.5555555555555</v>
+      </c>
+      <c r="F9">
+        <v>7</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>771.3333333333334</v>
+      </c>
+      <c r="F10">
+        <v>8</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>4</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>724.0</v>
+      </c>
+      <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>757.1111111111111</v>
+      </c>
+      <c r="F12">
+        <v>7</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13">
+        <v>759.7777777777778</v>
+      </c>
+      <c r="F13">
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>678.2222222222222</v>
+      </c>
+      <c r="F14">
+        <v>7</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>756.5555555555555</v>
+      </c>
+      <c r="F15">
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>2</v>
+      </c>
+      <c r="E16">
+        <v>761.4444444444445</v>
+      </c>
+      <c r="F16">
+        <v>8</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>724.0</v>
+      </c>
+      <c r="F17">
+        <v>8</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>2</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18">
+        <v>753.8888888888889</v>
+      </c>
+      <c r="F18">
+        <v>7</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>762.0</v>
+      </c>
+      <c r="F19">
+        <v>7</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>678.2222222222222</v>
+      </c>
+      <c r="F20">
+        <v>7</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>752.6666666666666</v>
+      </c>
+      <c r="F21">
+        <v>8</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>763.3333333333334</v>
+      </c>
+      <c r="F22">
+        <v>8</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>8</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>726.5555555555555</v>
+      </c>
+      <c r="F23">
+        <v>7</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>2</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>785.7777777777778</v>
+      </c>
+      <c r="F24">
+        <v>9</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>8</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>2</v>
+      </c>
+      <c r="E25">
+        <v>720.6666666666666</v>
+      </c>
+      <c r="F25">
+        <v>7</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>9</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>726.5555555555555</v>
+      </c>
+      <c r="F26">
+        <v>7</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>9</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>2</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>755.2222222222222</v>
+      </c>
+      <c r="F27">
+        <v>8</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>9</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>2</v>
+      </c>
+      <c r="E28">
+        <v>747.7777777777778</v>
+      </c>
+      <c r="F28">
+        <v>8</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>10</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>balanced</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>1</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="E29">
+        <v>678.2222222222222</v>
+      </c>
+      <c r="F29">
+        <v>7</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>10</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>shield_spend</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30">
+        <v>0</v>
+      </c>
+      <c r="E30">
+        <v>774.1111111111111</v>
+      </c>
+      <c r="F30">
+        <v>8</v>
+      </c>
+      <c r="G30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>10</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>shield_save</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31">
+        <v>2</v>
+      </c>
+      <c r="E31">
+        <v>730.5555555555555</v>
+      </c>
+      <c r="F31">
+        <v>8</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Lineups Used</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Lead Lineups Used</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Back Lineups Used</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Viable Lineup Rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>All Lineup Rate</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Best Lineup Score</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Pokemon</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Severity</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Message</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>